--- a/diseases/d013/2000-2004.xlsx
+++ b/diseases/d013/2000-2004.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -5009,9 +5006,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -5405,9 +5399,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -5849,9 +5840,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -6293,9 +6281,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -6737,9 +6722,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -7181,9 +7163,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -7625,9 +7604,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -8069,9 +8045,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -8513,9 +8486,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -8957,9 +8927,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -9401,9 +9368,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -9845,9 +9809,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -10289,9 +10250,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -10733,9 +10691,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -11129,9 +11084,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -11573,9 +11525,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -12017,9 +11966,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -12461,9 +12407,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -12905,9 +12848,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -13349,9 +13289,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -13793,9 +13730,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -14237,9 +14171,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -14681,9 +14612,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -15125,9 +15053,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -15569,9 +15494,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -16013,9 +15935,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -16457,9 +16376,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -16853,9 +16769,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -17297,9 +17210,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -17741,9 +17651,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -18185,9 +18092,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -18629,9 +18533,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -19073,9 +18974,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -19517,9 +19415,6 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
@@ -19961,9 +19856,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -20405,9 +20297,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -20849,9 +20738,6 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -21293,9 +21179,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
@@ -21737,9 +21620,6 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
@@ -22181,9 +22061,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -22577,9 +22454,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -23021,9 +22895,6 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
@@ -23465,9 +23336,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -23909,9 +23777,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -24353,9 +24218,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -24797,9 +24659,6 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
@@ -25241,9 +25100,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -25685,9 +25541,6 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
@@ -26129,9 +25982,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -26573,9 +26423,6 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -27017,9 +26864,6 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0</v>
       </c>
@@ -27459,9 +27303,6 @@
         <v>0</v>
       </c>
       <c r="O179" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q179" t="n">
         <v>0</v>
       </c>
       <c r="R179" t="n">
